--- a/hedge/hedge.xlsx
+++ b/hedge/hedge.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Havrankova\Dropbox\Tom_Zuzka\2_papers\paper_hedge\JOES_revision\web\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9C3E32-F6D4-4981-AC19-FF61FA32A337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{995E42A1-CC29-4221-ACC3-2776F678659C}"/>
@@ -91967,7 +91962,7 @@
   </sheetData>
   <autoFilter ref="A1:AC1020" xr:uid="{ADF9F923-D9DE-4185-826F-71C8C1E96B1D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>